--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135644399</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>135644372</v>
       </c>
       <c r="B3" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,56 +892,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135645703</v>
+        <v>135674363</v>
       </c>
       <c r="B4" t="n">
-        <v>57977</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779437</v>
+        <v>779390</v>
       </c>
       <c r="R4" t="n">
-        <v>7171122</v>
+        <v>7171230</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,33 +978,34 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645703</t>
+          <t>https://artportalen.se/Sighting/135674363</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135645576</v>
+        <v>135687307</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>80553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,45 +1013,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779284</v>
+        <v>779343</v>
       </c>
       <c r="R5" t="n">
-        <v>7171102</v>
+        <v>7171114</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1084,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>på en mycket grov gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,33 +1093,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645576</t>
+          <t>https://artportalen.se/Sighting/135687307</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135645631</v>
+        <v>135687031</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,16 +1128,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,23 +1150,23 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>779389</v>
+        <v>779410</v>
       </c>
       <c r="R6" t="n">
-        <v>7171073</v>
+        <v>7171076</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1200,14 +1200,14 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>ca 3,5cm högt och 2,5cm brett färskt bohål ca 1m upp i ihålig gammelgran. Ingen fågel observerad.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1215,55 +1215,59 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645631</t>
+          <t>https://artportalen.se/Sighting/135687031</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135644274</v>
+        <v>135645703</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1271,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779337</v>
+        <v>779437</v>
       </c>
       <c r="R7" t="n">
-        <v>7171282</v>
+        <v>7171122</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1315,7 +1319,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1333,44 +1336,48 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644274</t>
+          <t>https://artportalen.se/Sighting/135645703</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135644289</v>
+        <v>135645576</v>
       </c>
       <c r="B8" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1378,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779310</v>
+        <v>779284</v>
       </c>
       <c r="R8" t="n">
-        <v>7171327</v>
+        <v>7171102</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1416,13 +1423,17 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1440,44 +1451,48 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644289</t>
+          <t>https://artportalen.se/Sighting/135645576</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135644299</v>
+        <v>135645631</v>
       </c>
       <c r="B9" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1500,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>779301</v>
+        <v>779389</v>
       </c>
       <c r="R9" t="n">
-        <v>7171329</v>
+        <v>7171073</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1523,13 +1538,17 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1547,58 +1566,62 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644299</t>
+          <t>https://artportalen.se/Sighting/135645631</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135644315</v>
+        <v>135686660</v>
       </c>
       <c r="B10" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>779285</v>
+        <v>779508</v>
       </c>
       <c r="R10" t="n">
-        <v>7171329</v>
+        <v>7171044</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,82 +1653,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644315</t>
+          <t>https://artportalen.se/Sighting/135686660</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135644331</v>
+        <v>135686733</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779292</v>
+        <v>779493</v>
       </c>
       <c r="R11" t="n">
-        <v>7171317</v>
+        <v>7171037</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1737,82 +1768,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644331</t>
+          <t>https://artportalen.se/Sighting/135686733</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135644346</v>
+        <v>135686788</v>
       </c>
       <c r="B12" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>779273</v>
+        <v>779489</v>
       </c>
       <c r="R12" t="n">
-        <v>7171312</v>
+        <v>7171038</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1844,82 +1883,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644346</t>
+          <t>https://artportalen.se/Sighting/135686788</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135644354</v>
+        <v>135686801</v>
       </c>
       <c r="B13" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779254</v>
+        <v>779480</v>
       </c>
       <c r="R13" t="n">
-        <v>7171340</v>
+        <v>7171035</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1951,82 +1998,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644354</t>
+          <t>https://artportalen.se/Sighting/135686801</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135644362</v>
+        <v>135686816</v>
       </c>
       <c r="B14" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779240</v>
+        <v>779477</v>
       </c>
       <c r="R14" t="n">
-        <v>7171347</v>
+        <v>7171042</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2058,82 +2113,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>färska ringhack på två granar</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644362</t>
+          <t>https://artportalen.se/Sighting/135686816</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135645535</v>
+        <v>135686842</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779260</v>
+        <v>779466</v>
       </c>
       <c r="R15" t="n">
-        <v>7171313</v>
+        <v>7171050</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2165,82 +2228,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645535</t>
+          <t>https://artportalen.se/Sighting/135686842</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135645607</v>
+        <v>135686868</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779327</v>
+        <v>779459</v>
       </c>
       <c r="R16" t="n">
-        <v>7171084</v>
+        <v>7171051</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,90 +2343,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>färska ringhack på två granar</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645607</t>
+          <t>https://artportalen.se/Sighting/135686868</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135645689</v>
+        <v>135686922</v>
       </c>
       <c r="B17" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>779441</v>
+        <v>779440</v>
       </c>
       <c r="R17" t="n">
-        <v>7171126</v>
+        <v>7171055</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2387,82 +2458,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645689</t>
+          <t>https://artportalen.se/Sighting/135686922</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135645712</v>
+        <v>135687271</v>
       </c>
       <c r="B18" t="n">
-        <v>99242</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779410</v>
+        <v>779381</v>
       </c>
       <c r="R18" t="n">
-        <v>7171146</v>
+        <v>7171082</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2494,82 +2573,94 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645712</t>
+          <t>https://artportalen.se/Sighting/135687271</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135645723</v>
+        <v>135686496</v>
       </c>
       <c r="B19" t="n">
-        <v>99242</v>
+        <v>58141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779414</v>
+        <v>779497</v>
       </c>
       <c r="R19" t="n">
-        <v>7171161</v>
+        <v>7171103</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,62 +2692,66 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>observerade på ca 3 meters håll</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645723</t>
+          <t>https://artportalen.se/Sighting/135686496</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135645558</v>
+        <v>135644274</v>
       </c>
       <c r="B20" t="n">
-        <v>106379</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2670,10 +2765,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>779243</v>
+        <v>779337</v>
       </c>
       <c r="R20" t="n">
-        <v>7171283</v>
+        <v>7171282</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2731,6 +2826,3886 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644274</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135644289</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>779310</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7171327</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644289</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135644299</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>779301</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7171329</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644299</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135644315</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>779285</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7171329</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644315</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135644331</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>779292</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7171317</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644331</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135644346</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>779273</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7171312</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644346</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135644354</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>779254</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7171340</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644354</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135644362</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>779240</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7171347</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135644362</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135645535</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>779260</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7171313</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645535</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135645607</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>779327</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7171084</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645607</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135645689</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>779441</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7171126</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645689</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135645712</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>779410</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7171146</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645712</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135645723</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>779414</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7171161</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135645723</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135674315</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>779370</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7171259</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3st överblommade</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135674315</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135686143</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>779400</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7171195</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>6st överblommade/i blom</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686143</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135686226</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>779391</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7171183</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Riklig förekomst!</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686226</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135686284</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>779406</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7171169</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686284</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135686323</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>779417</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7171136</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>både överblommade och i blomning</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686323</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135686364</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>779419</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7171133</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>43 st blomstänglar - både överblommade och i blom</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686364</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135686393</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>779428</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7171114</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>ca 10 blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686393</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135686406</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>779446</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7171116</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686406</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135686471</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>779497</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7171099</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ca 20 st blomstänglar, både överblommade och i blom</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686471</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135686549</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>779498</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7171105</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ca 10 st blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686549</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135686562</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>779505</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7171108</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686562</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135686579</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>779503</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7171088</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686579</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135686629</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>779512</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7171084</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686629</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135686640</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>779546</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7171053</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686640</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135687090</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>779412</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7171079</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>25 st blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687090</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135687223</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>779408</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7171091</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>över 20 blomstänglar på liten yta</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687223</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135687250</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>779389</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7171092</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687250</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135687362</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>779339</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7171125</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>många blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687362</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135687374</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>779300</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7171138</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687374</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135687385</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>779294</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7171165</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687385</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>135687395</v>
+      </c>
+      <c r="B53" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>779295</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7171176</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687395</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>135687410</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>779337</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7171220</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687410</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>135645558</v>
+      </c>
+      <c r="B55" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>779243</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7171283</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135645558</t>
         </is>
@@ -2757,6 +6732,41 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ55"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135644399</v>
+        <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92043</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>779254</v>
+        <v>779398</v>
       </c>
       <c r="R2" t="n">
-        <v>7171323</v>
+        <v>7171220</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,67 +748,76 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644399</t>
+          <t>https://artportalen.se/Sighting/135724875</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135644372</v>
+        <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -886,58 +892,51 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644372</t>
+          <t>https://artportalen.se/Sighting/135644399</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135674363</v>
+        <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>79438</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779390</v>
+        <v>779327</v>
       </c>
       <c r="R4" t="n">
-        <v>7171230</v>
+        <v>7171318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,90 +966,95 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135674363</t>
+          <t>https://artportalen.se/Sighting/135724909</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135687307</v>
+        <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>80553</v>
+        <v>92387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779343</v>
+        <v>779254</v>
       </c>
       <c r="R5" t="n">
-        <v>7171114</v>
+        <v>7171323</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på en mycket grov gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,70 +1099,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687307</t>
+          <t>https://artportalen.se/Sighting/135644372</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135687031</v>
+        <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>57993</v>
+        <v>96481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>779410</v>
+        <v>779348</v>
       </c>
       <c r="R6" t="n">
-        <v>7171076</v>
+        <v>7171111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,21 +1184,26 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ca 3,5cm högt och 2,5cm brett färskt bohål ca 1m upp i ihålig gammelgran. Ingen fågel observerad.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1215,27 +1211,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687031</t>
+          <t>https://artportalen.se/Sighting/135724882</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135645703</v>
+        <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>96481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,45 +1239,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2812</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779437</v>
+        <v>779273</v>
       </c>
       <c r="R7" t="n">
-        <v>7171122</v>
+        <v>7171333</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,9 +1296,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,27 +1323,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645703</t>
+          <t>https://artportalen.se/Sighting/135724903</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135645576</v>
+        <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>87692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,45 +1351,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3639</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rutspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius ionophyllus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M. M. Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779284</v>
+        <v>779314</v>
       </c>
       <c r="R8" t="n">
-        <v>7171102</v>
+        <v>7171333</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1418,14 +1408,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,73 +1435,72 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645576</t>
+          <t>https://artportalen.se/Sighting/135724905</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135645631</v>
+        <v>135674363</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>779389</v>
+        <v>779390</v>
       </c>
       <c r="R9" t="n">
-        <v>7171073</v>
+        <v>7171230</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,87 +1532,75 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645631</t>
+          <t>https://artportalen.se/Sighting/135674363</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135686660</v>
+        <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>779508</v>
+        <v>779399</v>
       </c>
       <c r="R10" t="n">
-        <v>7171044</v>
+        <v>7171255</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,14 +1630,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,27 +1657,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686660</t>
+          <t>https://artportalen.se/Sighting/135724873</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135686733</v>
+        <v>135687307</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>80553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1698,31 +1685,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779493</v>
+        <v>779343</v>
       </c>
       <c r="R11" t="n">
-        <v>7171037</v>
+        <v>7171114</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1756,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>på en mycket grov gammal sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,6 +1765,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1796,16 +1783,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686733</t>
+          <t>https://artportalen.se/Sighting/135687307</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135686788</v>
+        <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>80553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,42 +1800,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>779489</v>
+        <v>779348</v>
       </c>
       <c r="R12" t="n">
-        <v>7171038</v>
+        <v>7171111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,14 +1857,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,27 +1884,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686788</t>
+          <t>https://artportalen.se/Sighting/135724881</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135686801</v>
+        <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>80553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1928,42 +1912,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779480</v>
+        <v>779371</v>
       </c>
       <c r="R13" t="n">
-        <v>7171035</v>
+        <v>7171122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1993,14 +1969,19 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,27 +1996,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686801</t>
+          <t>https://artportalen.se/Sighting/135724886</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135686816</v>
+        <v>135687031</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2043,16 +2024,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100048</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2065,7 +2046,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2075,10 +2056,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779477</v>
+        <v>779410</v>
       </c>
       <c r="R14" t="n">
-        <v>7171042</v>
+        <v>7171076</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2115,14 +2096,14 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska ringhack på två granar</t>
+          <t>ca 3,5cm högt och 2,5cm brett färskt bohål ca 1m upp i ihålig gammelgran. Ingen fågel observerad.</t>
         </is>
       </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="b">
         <v>0</v>
@@ -2141,33 +2122,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686816</t>
+          <t>https://artportalen.se/Sighting/135687031</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135686842</v>
+        <v>135645703</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2180,23 +2161,23 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779466</v>
+        <v>779437</v>
       </c>
       <c r="R15" t="n">
-        <v>7171050</v>
+        <v>7171122</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2226,11 +2207,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2245,24 +2221,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686842</t>
+          <t>https://artportalen.se/Sighting/135645703</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135686868</v>
+        <v>135645576</v>
       </c>
       <c r="B16" t="n">
         <v>57980</v>
@@ -2301,17 +2277,17 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779459</v>
+        <v>779284</v>
       </c>
       <c r="R16" t="n">
-        <v>7171051</v>
+        <v>7171102</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2345,7 +2321,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>färska ringhack på två granar</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,24 +2336,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686868</t>
+          <t>https://artportalen.se/Sighting/135645576</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135686922</v>
+        <v>135645631</v>
       </c>
       <c r="B17" t="n">
         <v>57980</v>
@@ -2416,17 +2392,17 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>779440</v>
+        <v>779389</v>
       </c>
       <c r="R17" t="n">
-        <v>7171055</v>
+        <v>7171073</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2436,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,24 +2451,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686922</t>
+          <t>https://artportalen.se/Sighting/135645631</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135687271</v>
+        <v>135686660</v>
       </c>
       <c r="B18" t="n">
         <v>57980</v>
@@ -2535,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779381</v>
+        <v>779508</v>
       </c>
       <c r="R18" t="n">
-        <v>7171082</v>
+        <v>7171044</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,16 +2577,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687271</t>
+          <t>https://artportalen.se/Sighting/135686660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135686496</v>
+        <v>135686733</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2618,33 +2594,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2654,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779497</v>
+        <v>779493</v>
       </c>
       <c r="R19" t="n">
-        <v>7171103</v>
+        <v>7171037</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,7 +2666,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>observerade på ca 3 meters håll</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,58 +2692,62 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686496</t>
+          <t>https://artportalen.se/Sighting/135686733</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135644274</v>
+        <v>135686788</v>
       </c>
       <c r="B20" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>779337</v>
+        <v>779489</v>
       </c>
       <c r="R20" t="n">
-        <v>7171282</v>
+        <v>7171038</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2803,82 +2779,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644274</t>
+          <t>https://artportalen.se/Sighting/135686788</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135644289</v>
+        <v>135686801</v>
       </c>
       <c r="B21" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>779310</v>
+        <v>779480</v>
       </c>
       <c r="R21" t="n">
-        <v>7171327</v>
+        <v>7171035</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2910,82 +2894,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644289</t>
+          <t>https://artportalen.se/Sighting/135686801</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135644299</v>
+        <v>135686816</v>
       </c>
       <c r="B22" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>779301</v>
+        <v>779477</v>
       </c>
       <c r="R22" t="n">
-        <v>7171329</v>
+        <v>7171042</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3017,82 +3009,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på två granar</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644299</t>
+          <t>https://artportalen.se/Sighting/135686816</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135644315</v>
+        <v>135686842</v>
       </c>
       <c r="B23" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>779285</v>
+        <v>779466</v>
       </c>
       <c r="R23" t="n">
-        <v>7171329</v>
+        <v>7171050</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3124,82 +3124,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644315</t>
+          <t>https://artportalen.se/Sighting/135686842</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135644331</v>
+        <v>135686868</v>
       </c>
       <c r="B24" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>779292</v>
+        <v>779459</v>
       </c>
       <c r="R24" t="n">
-        <v>7171317</v>
+        <v>7171051</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3231,82 +3239,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>färska ringhack på två granar</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644331</t>
+          <t>https://artportalen.se/Sighting/135686868</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135644346</v>
+        <v>135686922</v>
       </c>
       <c r="B25" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>779273</v>
+        <v>779440</v>
       </c>
       <c r="R25" t="n">
-        <v>7171312</v>
+        <v>7171055</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3338,82 +3354,90 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644346</t>
+          <t>https://artportalen.se/Sighting/135686922</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135644354</v>
+        <v>135687271</v>
       </c>
       <c r="B26" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>779254</v>
+        <v>779381</v>
       </c>
       <c r="R26" t="n">
-        <v>7171340</v>
+        <v>7171082</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,82 +3469,87 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644354</t>
+          <t>https://artportalen.se/Sighting/135687271</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135644362</v>
+        <v>135724885</v>
       </c>
       <c r="B27" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>779240</v>
+        <v>779383</v>
       </c>
       <c r="R27" t="n">
-        <v>7171347</v>
+        <v>7171092</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3547,87 +3576,105 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135644362</t>
+          <t>https://artportalen.se/Sighting/135724885</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135645535</v>
+        <v>135724898</v>
       </c>
       <c r="B28" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>779260</v>
+        <v>779275</v>
       </c>
       <c r="R28" t="n">
-        <v>7171313</v>
+        <v>7171328</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3654,87 +3701,105 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Skalade granar</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645535</t>
+          <t>https://artportalen.se/Sighting/135724898</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135645607</v>
+        <v>135724901</v>
       </c>
       <c r="B29" t="n">
-        <v>99269</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>779327</v>
+        <v>779269</v>
       </c>
       <c r="R29" t="n">
-        <v>7171084</v>
+        <v>7171332</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3761,95 +3826,109 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Skalade granar</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645607</t>
+          <t>https://artportalen.se/Sighting/135724901</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135645689</v>
+        <v>135686496</v>
       </c>
       <c r="B30" t="n">
-        <v>99269</v>
+        <v>58141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>779441</v>
+        <v>779497</v>
       </c>
       <c r="R30" t="n">
-        <v>7171126</v>
+        <v>7171103</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3881,82 +3960,87 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>observerade på ca 3 meters håll</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645689</t>
+          <t>https://artportalen.se/Sighting/135686496</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135645712</v>
+        <v>135724915</v>
       </c>
       <c r="B31" t="n">
-        <v>99269</v>
+        <v>58141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>779410</v>
+        <v>779350</v>
       </c>
       <c r="R31" t="n">
-        <v>7171146</v>
+        <v>7171268</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3983,42 +4067,56 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645712</t>
+          <t>https://artportalen.se/Sighting/135724915</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135645723</v>
+        <v>135644274</v>
       </c>
       <c r="B32" t="n">
         <v>99269</v>
@@ -4057,10 +4155,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>779414</v>
+        <v>779337</v>
       </c>
       <c r="R32" t="n">
-        <v>7171161</v>
+        <v>7171282</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4119,13 +4217,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135645723</t>
+          <t>https://artportalen.se/Sighting/135644274</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135674315</v>
+        <v>135644289</v>
       </c>
       <c r="B33" t="n">
         <v>99269</v>
@@ -4155,26 +4253,22 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>779370</v>
+        <v>779310</v>
       </c>
       <c r="R33" t="n">
-        <v>7171259</v>
+        <v>7171327</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4204,11 +4298,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3st överblommade</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4224,24 +4313,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135674315</t>
+          <t>https://artportalen.se/Sighting/135644289</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135686143</v>
+        <v>135644299</v>
       </c>
       <c r="B34" t="n">
         <v>99269</v>
@@ -4271,26 +4360,22 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>779400</v>
+        <v>779301</v>
       </c>
       <c r="R34" t="n">
-        <v>7171195</v>
+        <v>7171329</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4320,11 +4405,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>6st överblommade/i blom</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4340,24 +4420,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686143</t>
+          <t>https://artportalen.se/Sighting/135644299</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135686226</v>
+        <v>135644315</v>
       </c>
       <c r="B35" t="n">
         <v>99269</v>
@@ -4387,26 +4467,22 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>779391</v>
+        <v>779285</v>
       </c>
       <c r="R35" t="n">
-        <v>7171183</v>
+        <v>7171329</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4436,11 +4512,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Riklig förekomst!</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4456,24 +4527,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686226</t>
+          <t>https://artportalen.se/Sighting/135644315</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135686284</v>
+        <v>135644331</v>
       </c>
       <c r="B36" t="n">
         <v>99269</v>
@@ -4503,26 +4574,22 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>779406</v>
+        <v>779292</v>
       </c>
       <c r="R36" t="n">
-        <v>7171169</v>
+        <v>7171317</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4567,24 +4634,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686284</t>
+          <t>https://artportalen.se/Sighting/135644331</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135686323</v>
+        <v>135644346</v>
       </c>
       <c r="B37" t="n">
         <v>99269</v>
@@ -4614,26 +4681,22 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>779417</v>
+        <v>779273</v>
       </c>
       <c r="R37" t="n">
-        <v>7171136</v>
+        <v>7171312</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4663,11 +4726,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>både överblommade och i blomning</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4683,24 +4741,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686323</t>
+          <t>https://artportalen.se/Sighting/135644346</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135686364</v>
+        <v>135644354</v>
       </c>
       <c r="B38" t="n">
         <v>99269</v>
@@ -4730,26 +4788,22 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>779419</v>
+        <v>779254</v>
       </c>
       <c r="R38" t="n">
-        <v>7171133</v>
+        <v>7171340</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4779,11 +4833,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>43 st blomstänglar - både överblommade och i blom</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4799,24 +4848,24 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686364</t>
+          <t>https://artportalen.se/Sighting/135644354</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135686393</v>
+        <v>135644362</v>
       </c>
       <c r="B39" t="n">
         <v>99269</v>
@@ -4846,26 +4895,22 @@
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>779428</v>
+        <v>779240</v>
       </c>
       <c r="R39" t="n">
-        <v>7171114</v>
+        <v>7171347</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4895,11 +4940,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>ca 10 blomstänglar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4915,24 +4955,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686393</t>
+          <t>https://artportalen.se/Sighting/135644362</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135686406</v>
+        <v>135645535</v>
       </c>
       <c r="B40" t="n">
         <v>99269</v>
@@ -4962,26 +5002,22 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>779446</v>
+        <v>779260</v>
       </c>
       <c r="R40" t="n">
-        <v>7171116</v>
+        <v>7171313</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5026,24 +5062,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686406</t>
+          <t>https://artportalen.se/Sighting/135645535</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135686471</v>
+        <v>135645607</v>
       </c>
       <c r="B41" t="n">
         <v>99269</v>
@@ -5073,26 +5109,22 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>779497</v>
+        <v>779327</v>
       </c>
       <c r="R41" t="n">
-        <v>7171099</v>
+        <v>7171084</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5122,11 +5154,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>ca 20 st blomstänglar, både överblommade och i blom</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5142,24 +5169,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686471</t>
+          <t>https://artportalen.se/Sighting/135645607</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135686549</v>
+        <v>135645689</v>
       </c>
       <c r="B42" t="n">
         <v>99269</v>
@@ -5187,7 +5214,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
@@ -5198,17 +5229,17 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>779498</v>
+        <v>779441</v>
       </c>
       <c r="R42" t="n">
-        <v>7171105</v>
+        <v>7171126</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5238,11 +5269,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>ca 10 st blomstänglar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5258,24 +5284,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686549</t>
+          <t>https://artportalen.se/Sighting/135645689</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135686562</v>
+        <v>135645712</v>
       </c>
       <c r="B43" t="n">
         <v>99269</v>
@@ -5305,26 +5331,22 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>779505</v>
+        <v>779410</v>
       </c>
       <c r="R43" t="n">
-        <v>7171108</v>
+        <v>7171146</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5369,24 +5391,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686562</t>
+          <t>https://artportalen.se/Sighting/135645712</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135686579</v>
+        <v>135645723</v>
       </c>
       <c r="B44" t="n">
         <v>99269</v>
@@ -5415,27 +5437,23 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lilla-kvarnberget, Vb</t>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>779503</v>
+        <v>779414</v>
       </c>
       <c r="R44" t="n">
-        <v>7171088</v>
+        <v>7171161</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5480,24 +5498,24 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686579</t>
+          <t>https://artportalen.se/Sighting/135645723</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135686629</v>
+        <v>135674315</v>
       </c>
       <c r="B45" t="n">
         <v>99269</v>
@@ -5529,7 +5547,7 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5540,10 +5558,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>779512</v>
+        <v>779370</v>
       </c>
       <c r="R45" t="n">
-        <v>7171084</v>
+        <v>7171259</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5578,6 +5596,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>3st överblommade</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5602,13 +5625,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686629</t>
+          <t>https://artportalen.se/Sighting/135674315</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135686640</v>
+        <v>135686143</v>
       </c>
       <c r="B46" t="n">
         <v>99269</v>
@@ -5638,7 +5661,11 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
@@ -5647,10 +5674,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>779546</v>
+        <v>779400</v>
       </c>
       <c r="R46" t="n">
-        <v>7171053</v>
+        <v>7171195</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5685,6 +5712,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>6st överblommade/i blom</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5709,13 +5741,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135686640</t>
+          <t>https://artportalen.se/Sighting/135686143</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135687090</v>
+        <v>135686226</v>
       </c>
       <c r="B47" t="n">
         <v>99269</v>
@@ -5747,7 +5779,7 @@
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -5758,10 +5790,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>779412</v>
+        <v>779391</v>
       </c>
       <c r="R47" t="n">
-        <v>7171079</v>
+        <v>7171183</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5798,7 +5830,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>25 st blomstänglar</t>
+          <t>Riklig förekomst!</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5825,13 +5857,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687090</t>
+          <t>https://artportalen.se/Sighting/135686226</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135687223</v>
+        <v>135686284</v>
       </c>
       <c r="B48" t="n">
         <v>99269</v>
@@ -5863,7 +5895,7 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -5874,10 +5906,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>779408</v>
+        <v>779406</v>
       </c>
       <c r="R48" t="n">
-        <v>7171091</v>
+        <v>7171169</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5912,11 +5944,6 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>över 20 blomstänglar på liten yta</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -5941,13 +5968,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687223</t>
+          <t>https://artportalen.se/Sighting/135686284</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135687250</v>
+        <v>135686323</v>
       </c>
       <c r="B49" t="n">
         <v>99269</v>
@@ -5990,10 +6017,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>779389</v>
+        <v>779417</v>
       </c>
       <c r="R49" t="n">
-        <v>7171092</v>
+        <v>7171136</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6028,6 +6055,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>både överblommade och i blomning</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6052,13 +6084,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687250</t>
+          <t>https://artportalen.se/Sighting/135686323</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135687362</v>
+        <v>135686364</v>
       </c>
       <c r="B50" t="n">
         <v>99269</v>
@@ -6101,10 +6133,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>779339</v>
+        <v>779419</v>
       </c>
       <c r="R50" t="n">
-        <v>7171125</v>
+        <v>7171133</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6141,7 +6173,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>många blomstänglar</t>
+          <t>43 st blomstänglar - både överblommade och i blom</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6168,13 +6200,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687362</t>
+          <t>https://artportalen.se/Sighting/135686364</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135687374</v>
+        <v>135686393</v>
       </c>
       <c r="B51" t="n">
         <v>99269</v>
@@ -6204,7 +6236,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -6213,10 +6249,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>779300</v>
+        <v>779428</v>
       </c>
       <c r="R51" t="n">
-        <v>7171138</v>
+        <v>7171114</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6251,6 +6287,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ca 10 blomstänglar</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6275,13 +6316,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687374</t>
+          <t>https://artportalen.se/Sighting/135686393</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135687385</v>
+        <v>135686406</v>
       </c>
       <c r="B52" t="n">
         <v>99269</v>
@@ -6311,7 +6352,11 @@
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
@@ -6320,10 +6365,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>779294</v>
+        <v>779446</v>
       </c>
       <c r="R52" t="n">
-        <v>7171165</v>
+        <v>7171116</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6382,13 +6427,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687385</t>
+          <t>https://artportalen.se/Sighting/135686406</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135687395</v>
+        <v>135686471</v>
       </c>
       <c r="B53" t="n">
         <v>99269</v>
@@ -6418,7 +6463,11 @@
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -6427,10 +6476,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>779295</v>
+        <v>779497</v>
       </c>
       <c r="R53" t="n">
-        <v>7171176</v>
+        <v>7171099</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6465,6 +6514,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ca 20 st blomstänglar, både överblommade och i blom</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6489,13 +6543,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687395</t>
+          <t>https://artportalen.se/Sighting/135686471</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135687410</v>
+        <v>135686549</v>
       </c>
       <c r="B54" t="n">
         <v>99269</v>
@@ -6538,10 +6592,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>779337</v>
+        <v>779498</v>
       </c>
       <c r="R54" t="n">
-        <v>7171220</v>
+        <v>7171105</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6576,6 +6630,11 @@
           <t>2026-08-04</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>ca 10 st blomstänglar</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6600,58 +6659,62 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135687410</t>
+          <t>https://artportalen.se/Sighting/135686549</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135645558</v>
+        <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>106406</v>
+        <v>99269</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Renbergsvattnet kvarnberget, Vb</t>
+          <t>Lilla-kvarnberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>779243</v>
+        <v>779505</v>
       </c>
       <c r="R55" t="n">
-        <v>7171283</v>
+        <v>7171108</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6696,18 +6759,3026 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135686562</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135686579</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>779503</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7171088</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686579</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135686629</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>779512</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7171084</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686629</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135686640</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>779546</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7171053</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135686640</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135687090</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>779412</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7171079</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>25 st blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687090</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135687223</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>779408</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7171091</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>över 20 blomstänglar på liten yta</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687223</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135687250</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>779389</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7171092</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687250</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135687362</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>779339</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7171125</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>många blomstänglar</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687362</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135687374</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>779300</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7171138</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687374</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135687385</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>779294</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7171165</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687385</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135687395</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>779295</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7171176</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687395</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135687410</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lilla-kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>779337</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7171220</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135687410</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135724872</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>779372</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7171257</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724872</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135724877</v>
+      </c>
+      <c r="B68" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>779396</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7171189</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724877</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135724878</v>
+      </c>
+      <c r="B69" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>779385</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7171165</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724878</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135724880</v>
+      </c>
+      <c r="B70" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>779383</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7171153</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724880</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135724883</v>
+      </c>
+      <c r="B71" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>779348</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7171111</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724883</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135724890</v>
+      </c>
+      <c r="B72" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>779316</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7171120</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724890</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135724893</v>
+      </c>
+      <c r="B73" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>779254</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7171254</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724893</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135724895</v>
+      </c>
+      <c r="B74" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>779252</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7171289</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:53</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724895</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135724897</v>
+      </c>
+      <c r="B75" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>779251</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7171325</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724897</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135724900</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>779269</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7171332</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724900</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135724912</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>779340</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7171306</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724912</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135724914</v>
+      </c>
+      <c r="B78" t="n">
+        <v>99269</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>779347</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7171298</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724914</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135645558</v>
+      </c>
+      <c r="B79" t="n">
+        <v>106406</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Renbergsvattnet kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>779243</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7171283</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135645558</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135724906</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99291</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>779314</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7171333</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724906</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135724888</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98320</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>779345</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7171110</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724888</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135724910</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92435</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kvarnberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>779327</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7171318</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135724910</t>
         </is>
       </c>
     </row>
@@ -6767,6 +9838,33 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87695</v>
+        <v>87697</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>135644274</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135644289</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135644299</v>
       </c>
       <c r="B34" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135644315</v>
       </c>
       <c r="B35" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>135644331</v>
       </c>
       <c r="B36" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135644346</v>
       </c>
       <c r="B37" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135644354</v>
       </c>
       <c r="B38" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135644362</v>
       </c>
       <c r="B39" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>135645535</v>
       </c>
       <c r="B40" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>135645607</v>
       </c>
       <c r="B41" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135645689</v>
       </c>
       <c r="B42" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135645712</v>
       </c>
       <c r="B43" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135645723</v>
       </c>
       <c r="B44" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135645558</v>
       </c>
       <c r="B79" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98325</v>
+        <v>98327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87697</v>
+        <v>87699</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135674363</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135687307</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>135687031</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>57995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135645703</v>
       </c>
       <c r="B15" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>135645576</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135645631</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135686660</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>135686733</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135686788</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>135686801</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>135686816</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>135686842</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>135686868</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>135686922</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>135687271</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135724885</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>135724898</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>135724901</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135686496</v>
       </c>
       <c r="B30" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>135724915</v>
       </c>
       <c r="B31" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>135644274</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135644289</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135644299</v>
       </c>
       <c r="B34" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135644315</v>
       </c>
       <c r="B35" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>135644331</v>
       </c>
       <c r="B36" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135644346</v>
       </c>
       <c r="B37" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135644354</v>
       </c>
       <c r="B38" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135644362</v>
       </c>
       <c r="B39" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>135645535</v>
       </c>
       <c r="B40" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>135645607</v>
       </c>
       <c r="B41" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135645689</v>
       </c>
       <c r="B42" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135645712</v>
       </c>
       <c r="B43" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135645723</v>
       </c>
       <c r="B44" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135645558</v>
       </c>
       <c r="B79" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87699</v>
+        <v>87700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135674363</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135687307</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>135644274</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135644289</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135644299</v>
       </c>
       <c r="B34" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135644315</v>
       </c>
       <c r="B35" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>135644331</v>
       </c>
       <c r="B36" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135644346</v>
       </c>
       <c r="B37" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135644354</v>
       </c>
       <c r="B38" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135644362</v>
       </c>
       <c r="B39" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>135645535</v>
       </c>
       <c r="B40" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>135645607</v>
       </c>
       <c r="B41" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135645689</v>
       </c>
       <c r="B42" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135645712</v>
       </c>
       <c r="B43" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135645723</v>
       </c>
       <c r="B44" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135645558</v>
       </c>
       <c r="B79" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87700</v>
+        <v>87701</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>135644274</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135644289</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135644299</v>
       </c>
       <c r="B34" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135644315</v>
       </c>
       <c r="B35" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>135644331</v>
       </c>
       <c r="B36" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135644346</v>
       </c>
       <c r="B37" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135644354</v>
       </c>
       <c r="B38" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135644362</v>
       </c>
       <c r="B39" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>135645535</v>
       </c>
       <c r="B40" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>135645607</v>
       </c>
       <c r="B41" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135645689</v>
       </c>
       <c r="B42" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135645712</v>
       </c>
       <c r="B43" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135645723</v>
       </c>
       <c r="B44" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135645558</v>
       </c>
       <c r="B79" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87701</v>
+        <v>87702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135674363</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135687307</v>
       </c>
       <c r="B11" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>135687031</v>
       </c>
       <c r="B14" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135645703</v>
       </c>
       <c r="B15" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>135645576</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135645631</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135686660</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>135686733</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135686788</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>135686801</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>135686816</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>135686842</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>135686868</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>135686922</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>135687271</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135724885</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>135724898</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>135724901</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135686496</v>
       </c>
       <c r="B30" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>135724915</v>
       </c>
       <c r="B31" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>135644274</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135644289</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135644299</v>
       </c>
       <c r="B34" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135644315</v>
       </c>
       <c r="B35" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>135644331</v>
       </c>
       <c r="B36" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135644346</v>
       </c>
       <c r="B37" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135644354</v>
       </c>
       <c r="B38" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135644362</v>
       </c>
       <c r="B39" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>135645535</v>
       </c>
       <c r="B40" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>135645607</v>
       </c>
       <c r="B41" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135645689</v>
       </c>
       <c r="B42" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135645712</v>
       </c>
       <c r="B43" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135645723</v>
       </c>
       <c r="B44" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135645558</v>
       </c>
       <c r="B79" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135644399</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>135644372</v>
       </c>
       <c r="B5" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87702</v>
+        <v>87708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135674363</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135687307</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>135687031</v>
       </c>
       <c r="B14" t="n">
-        <v>57996</v>
+        <v>58000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>135645703</v>
       </c>
       <c r="B15" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>135645576</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>135645631</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135686660</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>135686733</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135686788</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>135686801</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>135686816</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>135686842</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>135686868</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>135686922</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>135687271</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135724885</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>135724898</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>135724901</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135686496</v>
       </c>
       <c r="B30" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>135724915</v>
       </c>
       <c r="B31" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>135644274</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         <v>135644289</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>135644299</v>
       </c>
       <c r="B34" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>135644315</v>
       </c>
       <c r="B35" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>135644331</v>
       </c>
       <c r="B36" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>135644346</v>
       </c>
       <c r="B37" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>135644354</v>
       </c>
       <c r="B38" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>135644362</v>
       </c>
       <c r="B39" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>135645535</v>
       </c>
       <c r="B40" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5130,7 +5130,7 @@
         <v>135645607</v>
       </c>
       <c r="B41" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>135645689</v>
       </c>
       <c r="B42" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>135645712</v>
       </c>
       <c r="B43" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5459,7 +5459,7 @@
         <v>135645723</v>
       </c>
       <c r="B44" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>135645558</v>
       </c>
       <c r="B79" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92023</v>
+        <v>92024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87708</v>
+        <v>87709</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>135674363</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135687307</v>
       </c>
       <c r="B11" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>135687031</v>
       </c>
       <c r="B14" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>135686660</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>135686733</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>135686788</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>135686801</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>135686816</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>135686842</v>
       </c>
       <c r="B23" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>135686868</v>
       </c>
       <c r="B24" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>135686922</v>
       </c>
       <c r="B25" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>135687271</v>
       </c>
       <c r="B26" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135724885</v>
       </c>
       <c r="B27" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>135724898</v>
       </c>
       <c r="B28" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>135724901</v>
       </c>
       <c r="B29" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>135686496</v>
       </c>
       <c r="B30" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>135724915</v>
       </c>
       <c r="B31" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>135674315</v>
       </c>
       <c r="B45" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>135686143</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>135686226</v>
       </c>
       <c r="B47" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>135686284</v>
       </c>
       <c r="B48" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6025,7 +6025,7 @@
         <v>135686323</v>
       </c>
       <c r="B49" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>135686364</v>
       </c>
       <c r="B50" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>135686393</v>
       </c>
       <c r="B51" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>135686406</v>
       </c>
       <c r="B52" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>135686471</v>
       </c>
       <c r="B53" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>135686549</v>
       </c>
       <c r="B54" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>135686562</v>
       </c>
       <c r="B55" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>135686579</v>
       </c>
       <c r="B56" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>135686629</v>
       </c>
       <c r="B57" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>135686640</v>
       </c>
       <c r="B58" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>135687090</v>
       </c>
       <c r="B59" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>135687223</v>
       </c>
       <c r="B60" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>135687250</v>
       </c>
       <c r="B61" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>135687362</v>
       </c>
       <c r="B62" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>135687374</v>
       </c>
       <c r="B63" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         <v>135687385</v>
       </c>
       <c r="B64" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>135687395</v>
       </c>
       <c r="B65" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>135687410</v>
       </c>
       <c r="B66" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92465</v>
+        <v>92466</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87709</v>
+        <v>87715</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92466</v>
+        <v>92472</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135724905</v>
       </c>
       <c r="B8" t="n">
-        <v>87715</v>
+        <v>87722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135724873</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135724881</v>
       </c>
       <c r="B12" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>135724886</v>
       </c>
       <c r="B13" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>135724885</v>
       </c>
       <c r="B27" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>135724898</v>
       </c>
       <c r="B28" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>135724901</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>135724915</v>
       </c>
       <c r="B31" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92472</v>
+        <v>92479</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 61636-2025 artfynd.xlsx
+++ b/artfynd/A 61636-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135724875</v>
       </c>
       <c r="B2" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135724909</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>135724882</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135724903</v>
       </c>
       <c r="B7" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>135724872</v>
       </c>
       <c r="B67" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>135724877</v>
       </c>
       <c r="B68" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>135724878</v>
       </c>
       <c r="B69" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>135724880</v>
       </c>
       <c r="B70" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>135724883</v>
       </c>
       <c r="B71" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135724890</v>
       </c>
       <c r="B72" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>135724893</v>
       </c>
       <c r="B73" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v>135724895</v>
       </c>
       <c r="B74" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>135724897</v>
       </c>
       <c r="B75" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>135724900</v>
       </c>
       <c r="B76" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>135724912</v>
       </c>
       <c r="B77" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>135724914</v>
       </c>
       <c r="B78" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>135724906</v>
       </c>
       <c r="B80" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>135724888</v>
       </c>
       <c r="B81" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>135724910</v>
       </c>
       <c r="B82" t="n">
-        <v>92479</v>
+        <v>92480</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
